--- a/scripts/fixtures/sample.xlsx
+++ b/scripts/fixtures/sample.xlsx
@@ -397,55 +397,80 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:C9"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>Nombre</v>
-      </c>
-      <c r="B1" t="str">
-        <v>Edad</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Activo</v>
+        <v>Metadato 1</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Ana</v>
-      </c>
-      <c r="B2">
-        <v>30</v>
-      </c>
-      <c r="C2" t="b">
-        <v>1</v>
+        <v>Metadato 2</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Luis</v>
-      </c>
-      <c r="B3">
-        <v>25</v>
-      </c>
-      <c r="C3" t="b">
-        <v>0</v>
+        <v>Metadato 3</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
+        <v>Metadato 4</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>Metadato 5</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>Nombre</v>
+      </c>
+      <c r="B6" t="str">
+        <v>Edad</v>
+      </c>
+      <c r="C6" t="str">
+        <v>Activo</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>Ana</v>
+      </c>
+      <c r="B7">
+        <v>30</v>
+      </c>
+      <c r="C7" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>Luis</v>
+      </c>
+      <c r="B8">
+        <v>25</v>
+      </c>
+      <c r="C8" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
         <v>María</v>
       </c>
-      <c r="B4">
+      <c r="B9">
         <v>35</v>
       </c>
-      <c r="C4" t="b">
+      <c r="C9" t="b">
         <v>1</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C4"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C9"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/scripts/fixtures/sample.xlsx
+++ b/scripts/fixtures/sample.xlsx
@@ -397,80 +397,100 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C9"/>
+  <dimension ref="A2:E11"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Metadato 1</v>
-      </c>
-    </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Metadato 2</v>
+        <v/>
+      </c>
+      <c r="B2" t="str">
+        <v/>
+      </c>
+      <c r="C2" t="str">
+        <v>EMPRESA:</v>
+      </c>
+      <c r="D2" t="str">
+        <v>COD001</v>
+      </c>
+      <c r="E2" t="str">
+        <v>Mi Empresa SA</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Metadato 3</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>Metadato 4</v>
+        <v/>
+      </c>
+      <c r="B3" t="str">
+        <v/>
+      </c>
+      <c r="C3" t="str">
+        <v>SELECCIÓN</v>
+      </c>
+      <c r="D3" t="str">
+        <v>Todos los registros</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Metadato 5</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>Nombre</v>
-      </c>
-      <c r="B6" t="str">
-        <v>Edad</v>
-      </c>
-      <c r="C6" t="str">
-        <v>Activo</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>Ana</v>
-      </c>
-      <c r="B7">
-        <v>30</v>
-      </c>
-      <c r="C7" t="b">
-        <v>1</v>
+        <v/>
+      </c>
+      <c r="B5" t="str">
+        <v/>
+      </c>
+      <c r="C5" t="str">
+        <v>FECHA:</v>
+      </c>
+      <c r="D5" t="str">
+        <v>15/01/2025</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>Luis</v>
-      </c>
-      <c r="B8">
-        <v>25</v>
-      </c>
-      <c r="C8" t="b">
-        <v>0</v>
+        <v>Nombre</v>
+      </c>
+      <c r="B8" t="str">
+        <v>Edad</v>
+      </c>
+      <c r="C8" t="str">
+        <v>Activo</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>María</v>
+        <v>Ana</v>
       </c>
       <c r="B9">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="C9" t="b">
         <v>1</v>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>Luis</v>
+      </c>
+      <c r="B10">
+        <v>25</v>
+      </c>
+      <c r="C10" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>María</v>
+      </c>
+      <c r="B11">
+        <v>35</v>
+      </c>
+      <c r="C11" t="b">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C9"/>
+    <ignoredError numberStoredAsText="1" sqref="A2:E11"/>
   </ignoredErrors>
 </worksheet>
 </file>